--- a/서버정보/20260706_리소스배포_운영.xlsx
+++ b/서버정보/20260706_리소스배포_운영.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31647AFC-2CFD-4AFF-AB93-56BEDB907F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39452D3-83B6-47A1-87A9-63AA7C09ADBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,6 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">LB!$B$1:$Q$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">LB_Probe!$B$1:$K$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">LB_Rule!$B$1:$S$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">NSG!$B$1:$M$161</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -6237,7 +6238,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6596,15 +6597,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -25524,11 +25516,11 @@
       <c r="B143" s="95" t="s">
         <v>1100</v>
       </c>
-      <c r="C143" s="120" t="str" cm="1">
+      <c r="C143" s="95" t="str" cm="1">
         <f t="array" ref="C143">UPPER(INDEX(_xlfn.TEXTSPLIT($D143, "-"), 3))</f>
         <v>COMM</v>
       </c>
-      <c r="D143" s="120" t="s">
+      <c r="D143" s="95" t="s">
         <v>231</v>
       </c>
       <c r="E143" s="95" t="s">
@@ -25561,7 +25553,7 @@
       <c r="N143" s="114" t="s">
         <v>1066</v>
       </c>
-      <c r="O143" s="121" t="str">
+      <c r="O143" s="115" t="str">
         <f>SUBSTITUTE(F143,"hazr-","")&amp;"-osdisk"</f>
         <v>l-com-scmsol01-osdisk</v>
       </c>
@@ -25571,10 +25563,10 @@
       <c r="Q143" s="117" t="s">
         <v>179</v>
       </c>
-      <c r="R143" s="120"/>
+      <c r="R143" s="95"/>
       <c r="S143" s="95"/>
-      <c r="T143" s="120"/>
-      <c r="U143" s="120" t="str">
+      <c r="T143" s="95"/>
+      <c r="U143" s="95" t="str">
         <f>SUBSTITUTE(F143,"hazr-","")&amp;"-nic"</f>
         <v>l-com-scmsol01-nic</v>
       </c>
@@ -25587,10 +25579,10 @@
       <c r="X143" s="95" t="s">
         <v>231</v>
       </c>
-      <c r="Y143" s="122" t="s">
+      <c r="Y143" s="95" t="s">
         <v>223</v>
       </c>
-      <c r="Z143" s="122" t="s">
+      <c r="Z143" s="95" t="s">
         <v>1043</v>
       </c>
       <c r="AA143" s="95" t="b">
@@ -33821,56 +33813,56 @@
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155" s="99"/>
-      <c r="B155" s="123" t="s">
+      <c r="B155" s="120" t="s">
         <v>1100</v>
       </c>
-      <c r="C155" s="123" t="str" cm="1">
+      <c r="C155" s="120" t="str" cm="1">
         <f t="array" ref="C155">UPPER(INDEX(_xlfn.TEXTSPLIT($D155, "-"), 3))</f>
         <v>SEC</v>
       </c>
-      <c r="D155" s="124" t="s">
+      <c r="D155" s="121" t="s">
         <v>1086</v>
       </c>
-      <c r="E155" s="125" t="s">
+      <c r="E155" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="F155" s="123" t="s">
+      <c r="F155" s="120" t="s">
         <v>1088</v>
       </c>
-      <c r="G155" s="123" t="s">
+      <c r="G155" s="120" t="s">
         <v>1098</v>
       </c>
-      <c r="H155" s="123" t="s">
+      <c r="H155" s="120" t="s">
         <v>179</v>
       </c>
-      <c r="I155" s="123">
+      <c r="I155" s="120">
         <v>128</v>
       </c>
-      <c r="J155" s="123" t="s">
+      <c r="J155" s="120" t="s">
         <v>1099</v>
       </c>
-      <c r="K155" s="123" t="s">
+      <c r="K155" s="120" t="s">
         <v>179</v>
       </c>
-      <c r="L155" s="123">
+      <c r="L155" s="120">
         <v>256</v>
       </c>
-      <c r="M155" s="124">
-        <v>1</v>
-      </c>
-      <c r="N155" s="123" t="s">
+      <c r="M155" s="121">
+        <v>1</v>
+      </c>
+      <c r="N155" s="120" t="s">
         <v>191</v>
       </c>
-      <c r="O155" s="123" t="s">
+      <c r="O155" s="120" t="s">
         <v>1086</v>
       </c>
-      <c r="P155" s="123" t="s">
+      <c r="P155" s="120" t="s">
         <v>1095</v>
       </c>
-      <c r="Q155" s="123" t="b">
-        <v>1</v>
-      </c>
-      <c r="R155" s="123"/>
+      <c r="Q155" s="120" t="b">
+        <v>1</v>
+      </c>
+      <c r="R155" s="120"/>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B156" s="74" t="s">
@@ -39469,7 +39461,7 @@
     <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="90"/>
       <c r="B139" s="80" t="s">
-        <v>1040</v>
+        <v>1100</v>
       </c>
       <c r="C139" s="80" t="str" cm="1">
         <f t="array" ref="C139">UPPER(INDEX(_xlfn.TEXTSPLIT($E139, "-"), 2))</f>
@@ -39509,7 +39501,7 @@
     <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="90"/>
       <c r="B140" s="78" t="s">
-        <v>1040</v>
+        <v>1100</v>
       </c>
       <c r="C140" s="78" t="str" cm="1">
         <f t="array" ref="C140">UPPER(INDEX(_xlfn.TEXTSPLIT($E140, "-"), 2))</f>
@@ -39947,10 +39939,7 @@
       <c r="B153" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="C153" s="80" t="str" cm="1">
-        <f t="array" ref="C153">UPPER(INDEX(_xlfn.TEXTSPLIT($E153, "-"), 2))</f>
-        <v>COM</v>
-      </c>
+      <c r="C153" s="80"/>
       <c r="D153" s="80" t="s">
         <v>323</v>
       </c>
@@ -39980,10 +39969,7 @@
       <c r="B154" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="C154" s="78" t="str" cm="1">
-        <f t="array" ref="C154">UPPER(INDEX(_xlfn.TEXTSPLIT($E154, "-"), 2))</f>
-        <v>COM</v>
-      </c>
+      <c r="C154" s="78"/>
       <c r="D154" s="78" t="s">
         <v>323</v>
       </c>
@@ -40260,6 +40246,7 @@
       <c r="M161" s="74"/>
     </row>
   </sheetData>
+  <autoFilter ref="B1:M161" xr:uid="{BAB1F184-7BFC-47CB-AC71-63C76B7E3D12}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -47057,6 +47044,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -47200,35 +47202,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -47250,9 +47227,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260706_리소스배포_운영.xlsx
+++ b/서버정보/20260706_리소스배포_운영.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39452D3-83B6-47A1-87A9-63AA7C09ADBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E106CEF-E7F6-4E64-9C42-9E1D8F02FA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,6 +29,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">LB_Probe!$B$1:$K$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">LB_Rule!$B$1:$S$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">NSG!$B$1:$M$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">VM_Datadisk!$B$1:$R$156</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -7802,7 +7803,7 @@
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="30"/>
     <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="29">
-      <calculatedColumnFormula array="1">UPPER(INDEX(_xlfn.TEXTSPLIT($D2, "-"), 3))</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">UPPER(INDEX(_xlfn.TEXTSPLIT($F2, "-"), 3))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="28"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="27"/>
@@ -12980,8 +12981,8 @@
       <c r="B2" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="74" t="str" cm="1">
-        <f t="array" ref="C2">UPPER(INDEX(_xlfn.TEXTSPLIT($D2, "-"), 3))</f>
+      <c r="C2" s="95" t="str" cm="1">
+        <f t="array" ref="C2">UPPER(INDEX(_xlfn.TEXTSPLIT($F2, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D2" s="80" t="s">
@@ -13069,8 +13070,8 @@
       <c r="B3" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="74" t="str" cm="1">
-        <f t="array" ref="C3">UPPER(INDEX(_xlfn.TEXTSPLIT($D3, "-"), 3))</f>
+      <c r="C3" s="95" t="str" cm="1">
+        <f t="array" ref="C3">UPPER(INDEX(_xlfn.TEXTSPLIT($F3, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D3" s="80" t="s">
@@ -13158,8 +13159,8 @@
       <c r="B4" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="74" t="str" cm="1">
-        <f t="array" ref="C4">UPPER(INDEX(_xlfn.TEXTSPLIT($D4, "-"), 3))</f>
+      <c r="C4" s="95" t="str" cm="1">
+        <f t="array" ref="C4">UPPER(INDEX(_xlfn.TEXTSPLIT($F4, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D4" s="80" t="s">
@@ -13247,8 +13248,8 @@
       <c r="B5" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="74" t="str" cm="1">
-        <f t="array" ref="C5">UPPER(INDEX(_xlfn.TEXTSPLIT($D5, "-"), 3))</f>
+      <c r="C5" s="95" t="str" cm="1">
+        <f t="array" ref="C5">UPPER(INDEX(_xlfn.TEXTSPLIT($F5, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D5" s="80" t="s">
@@ -13336,8 +13337,8 @@
       <c r="B6" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="74" t="str" cm="1">
-        <f t="array" ref="C6">UPPER(INDEX(_xlfn.TEXTSPLIT($D6, "-"), 3))</f>
+      <c r="C6" s="95" t="str" cm="1">
+        <f t="array" ref="C6">UPPER(INDEX(_xlfn.TEXTSPLIT($F6, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D6" s="80" t="s">
@@ -13425,8 +13426,8 @@
       <c r="B7" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="74" t="str" cm="1">
-        <f t="array" ref="C7">UPPER(INDEX(_xlfn.TEXTSPLIT($D7, "-"), 3))</f>
+      <c r="C7" s="95" t="str" cm="1">
+        <f t="array" ref="C7">UPPER(INDEX(_xlfn.TEXTSPLIT($F7, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D7" s="80" t="s">
@@ -13514,8 +13515,8 @@
       <c r="B8" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="74" t="str" cm="1">
-        <f t="array" ref="C8">UPPER(INDEX(_xlfn.TEXTSPLIT($D8, "-"), 3))</f>
+      <c r="C8" s="95" t="str" cm="1">
+        <f t="array" ref="C8">UPPER(INDEX(_xlfn.TEXTSPLIT($F8, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D8" s="80" t="s">
@@ -13603,8 +13604,8 @@
       <c r="B9" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="74" t="str" cm="1">
-        <f t="array" ref="C9">UPPER(INDEX(_xlfn.TEXTSPLIT($D9, "-"), 3))</f>
+      <c r="C9" s="95" t="str" cm="1">
+        <f t="array" ref="C9">UPPER(INDEX(_xlfn.TEXTSPLIT($F9, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D9" s="80" t="s">
@@ -13692,8 +13693,8 @@
       <c r="B10" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="74" t="str" cm="1">
-        <f t="array" ref="C10">UPPER(INDEX(_xlfn.TEXTSPLIT($D10, "-"), 3))</f>
+      <c r="C10" s="95" t="str" cm="1">
+        <f t="array" ref="C10">UPPER(INDEX(_xlfn.TEXTSPLIT($F10, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D10" s="80" t="s">
@@ -13781,8 +13782,8 @@
       <c r="B11" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="74" t="str" cm="1">
-        <f t="array" ref="C11">UPPER(INDEX(_xlfn.TEXTSPLIT($D11, "-"), 3))</f>
+      <c r="C11" s="95" t="str" cm="1">
+        <f t="array" ref="C11">UPPER(INDEX(_xlfn.TEXTSPLIT($F11, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D11" s="80" t="s">
@@ -13870,8 +13871,8 @@
       <c r="B12" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="74" t="str" cm="1">
-        <f t="array" ref="C12">UPPER(INDEX(_xlfn.TEXTSPLIT($D12, "-"), 3))</f>
+      <c r="C12" s="95" t="str" cm="1">
+        <f t="array" ref="C12">UPPER(INDEX(_xlfn.TEXTSPLIT($F12, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D12" s="80" t="s">
@@ -13959,8 +13960,8 @@
       <c r="B13" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="74" t="str" cm="1">
-        <f t="array" ref="C13">UPPER(INDEX(_xlfn.TEXTSPLIT($D13, "-"), 3))</f>
+      <c r="C13" s="95" t="str" cm="1">
+        <f t="array" ref="C13">UPPER(INDEX(_xlfn.TEXTSPLIT($F13, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D13" s="80" t="s">
@@ -14048,8 +14049,8 @@
       <c r="B14" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="74" t="str" cm="1">
-        <f t="array" ref="C14">UPPER(INDEX(_xlfn.TEXTSPLIT($D14, "-"), 3))</f>
+      <c r="C14" s="95" t="str" cm="1">
+        <f t="array" ref="C14">UPPER(INDEX(_xlfn.TEXTSPLIT($F14, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D14" s="80" t="s">
@@ -14137,8 +14138,8 @@
       <c r="B15" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="74" t="str" cm="1">
-        <f t="array" ref="C15">UPPER(INDEX(_xlfn.TEXTSPLIT($D15, "-"), 3))</f>
+      <c r="C15" s="95" t="str" cm="1">
+        <f t="array" ref="C15">UPPER(INDEX(_xlfn.TEXTSPLIT($F15, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D15" s="80" t="s">
@@ -14226,8 +14227,8 @@
       <c r="B16" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="74" t="str" cm="1">
-        <f t="array" ref="C16">UPPER(INDEX(_xlfn.TEXTSPLIT($D16, "-"), 3))</f>
+      <c r="C16" s="95" t="str" cm="1">
+        <f t="array" ref="C16">UPPER(INDEX(_xlfn.TEXTSPLIT($F16, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D16" s="80" t="s">
@@ -14315,8 +14316,8 @@
       <c r="B17" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="74" t="str" cm="1">
-        <f t="array" ref="C17">UPPER(INDEX(_xlfn.TEXTSPLIT($D17, "-"), 3))</f>
+      <c r="C17" s="95" t="str" cm="1">
+        <f t="array" ref="C17">UPPER(INDEX(_xlfn.TEXTSPLIT($F17, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D17" s="80" t="s">
@@ -14404,8 +14405,8 @@
       <c r="B18" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="74" t="str" cm="1">
-        <f t="array" ref="C18">UPPER(INDEX(_xlfn.TEXTSPLIT($D18, "-"), 3))</f>
+      <c r="C18" s="95" t="str" cm="1">
+        <f t="array" ref="C18">UPPER(INDEX(_xlfn.TEXTSPLIT($F18, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D18" s="80" t="s">
@@ -14493,8 +14494,8 @@
       <c r="B19" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="74" t="str" cm="1">
-        <f t="array" ref="C19">UPPER(INDEX(_xlfn.TEXTSPLIT($D19, "-"), 3))</f>
+      <c r="C19" s="95" t="str" cm="1">
+        <f t="array" ref="C19">UPPER(INDEX(_xlfn.TEXTSPLIT($F19, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D19" s="80" t="s">
@@ -14582,8 +14583,8 @@
       <c r="B20" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="74" t="str" cm="1">
-        <f t="array" ref="C20">UPPER(INDEX(_xlfn.TEXTSPLIT($D20, "-"), 3))</f>
+      <c r="C20" s="95" t="str" cm="1">
+        <f t="array" ref="C20">UPPER(INDEX(_xlfn.TEXTSPLIT($F20, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D20" s="80" t="s">
@@ -14671,8 +14672,8 @@
       <c r="B21" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="74" t="str" cm="1">
-        <f t="array" ref="C21">UPPER(INDEX(_xlfn.TEXTSPLIT($D21, "-"), 3))</f>
+      <c r="C21" s="95" t="str" cm="1">
+        <f t="array" ref="C21">UPPER(INDEX(_xlfn.TEXTSPLIT($F21, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D21" s="80" t="s">
@@ -14760,8 +14761,8 @@
       <c r="B22" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="74" t="str" cm="1">
-        <f t="array" ref="C22">UPPER(INDEX(_xlfn.TEXTSPLIT($D22, "-"), 3))</f>
+      <c r="C22" s="95" t="str" cm="1">
+        <f t="array" ref="C22">UPPER(INDEX(_xlfn.TEXTSPLIT($F22, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D22" s="80" t="s">
@@ -14849,8 +14850,8 @@
       <c r="B23" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="74" t="str" cm="1">
-        <f t="array" ref="C23">UPPER(INDEX(_xlfn.TEXTSPLIT($D23, "-"), 3))</f>
+      <c r="C23" s="95" t="str" cm="1">
+        <f t="array" ref="C23">UPPER(INDEX(_xlfn.TEXTSPLIT($F23, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D23" s="80" t="s">
@@ -14938,8 +14939,8 @@
       <c r="B24" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="74" t="str" cm="1">
-        <f t="array" ref="C24">UPPER(INDEX(_xlfn.TEXTSPLIT($D24, "-"), 3))</f>
+      <c r="C24" s="95" t="str" cm="1">
+        <f t="array" ref="C24">UPPER(INDEX(_xlfn.TEXTSPLIT($F24, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D24" s="80" t="s">
@@ -15027,8 +15028,8 @@
       <c r="B25" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="74" t="str" cm="1">
-        <f t="array" ref="C25">UPPER(INDEX(_xlfn.TEXTSPLIT($D25, "-"), 3))</f>
+      <c r="C25" s="95" t="str" cm="1">
+        <f t="array" ref="C25">UPPER(INDEX(_xlfn.TEXTSPLIT($F25, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D25" s="80" t="s">
@@ -15116,8 +15117,8 @@
       <c r="B26" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="74" t="str" cm="1">
-        <f t="array" ref="C26">UPPER(INDEX(_xlfn.TEXTSPLIT($D26, "-"), 3))</f>
+      <c r="C26" s="95" t="str" cm="1">
+        <f t="array" ref="C26">UPPER(INDEX(_xlfn.TEXTSPLIT($F26, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D26" s="80" t="s">
@@ -15205,8 +15206,8 @@
       <c r="B27" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="74" t="str" cm="1">
-        <f t="array" ref="C27">UPPER(INDEX(_xlfn.TEXTSPLIT($D27, "-"), 3))</f>
+      <c r="C27" s="95" t="str" cm="1">
+        <f t="array" ref="C27">UPPER(INDEX(_xlfn.TEXTSPLIT($F27, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D27" s="80" t="s">
@@ -15294,8 +15295,8 @@
       <c r="B28" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="74" t="str" cm="1">
-        <f t="array" ref="C28">UPPER(INDEX(_xlfn.TEXTSPLIT($D28, "-"), 3))</f>
+      <c r="C28" s="95" t="str" cm="1">
+        <f t="array" ref="C28">UPPER(INDEX(_xlfn.TEXTSPLIT($F28, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D28" s="80" t="s">
@@ -15383,8 +15384,8 @@
       <c r="B29" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="74" t="str" cm="1">
-        <f t="array" ref="C29">UPPER(INDEX(_xlfn.TEXTSPLIT($D29, "-"), 3))</f>
+      <c r="C29" s="95" t="str" cm="1">
+        <f t="array" ref="C29">UPPER(INDEX(_xlfn.TEXTSPLIT($F29, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D29" s="80" t="s">
@@ -15472,8 +15473,8 @@
       <c r="B30" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="74" t="str" cm="1">
-        <f t="array" ref="C30">UPPER(INDEX(_xlfn.TEXTSPLIT($D30, "-"), 3))</f>
+      <c r="C30" s="95" t="str" cm="1">
+        <f t="array" ref="C30">UPPER(INDEX(_xlfn.TEXTSPLIT($F30, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D30" s="80" t="s">
@@ -15561,8 +15562,8 @@
       <c r="B31" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="74" t="str" cm="1">
-        <f t="array" ref="C31">UPPER(INDEX(_xlfn.TEXTSPLIT($D31, "-"), 3))</f>
+      <c r="C31" s="95" t="str" cm="1">
+        <f t="array" ref="C31">UPPER(INDEX(_xlfn.TEXTSPLIT($F31, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D31" s="80" t="s">
@@ -15650,8 +15651,8 @@
       <c r="B32" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="74" t="str" cm="1">
-        <f t="array" ref="C32">UPPER(INDEX(_xlfn.TEXTSPLIT($D32, "-"), 3))</f>
+      <c r="C32" s="95" t="str" cm="1">
+        <f t="array" ref="C32">UPPER(INDEX(_xlfn.TEXTSPLIT($F32, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D32" s="80" t="s">
@@ -15739,8 +15740,8 @@
       <c r="B33" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="74" t="str" cm="1">
-        <f t="array" ref="C33">UPPER(INDEX(_xlfn.TEXTSPLIT($D33, "-"), 3))</f>
+      <c r="C33" s="95" t="str" cm="1">
+        <f t="array" ref="C33">UPPER(INDEX(_xlfn.TEXTSPLIT($F33, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D33" s="80" t="s">
@@ -15828,8 +15829,8 @@
       <c r="B34" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C34" s="74" t="str" cm="1">
-        <f t="array" ref="C34">UPPER(INDEX(_xlfn.TEXTSPLIT($D34, "-"), 3))</f>
+      <c r="C34" s="95" t="str" cm="1">
+        <f t="array" ref="C34">UPPER(INDEX(_xlfn.TEXTSPLIT($F34, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D34" s="80" t="s">
@@ -15917,8 +15918,8 @@
       <c r="B35" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="74" t="str" cm="1">
-        <f t="array" ref="C35">UPPER(INDEX(_xlfn.TEXTSPLIT($D35, "-"), 3))</f>
+      <c r="C35" s="95" t="str" cm="1">
+        <f t="array" ref="C35">UPPER(INDEX(_xlfn.TEXTSPLIT($F35, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D35" s="80" t="s">
@@ -16006,8 +16007,8 @@
       <c r="B36" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="74" t="str" cm="1">
-        <f t="array" ref="C36">UPPER(INDEX(_xlfn.TEXTSPLIT($D36, "-"), 3))</f>
+      <c r="C36" s="95" t="str" cm="1">
+        <f t="array" ref="C36">UPPER(INDEX(_xlfn.TEXTSPLIT($F36, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D36" s="80" t="s">
@@ -16095,8 +16096,8 @@
       <c r="B37" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="74" t="str" cm="1">
-        <f t="array" ref="C37">UPPER(INDEX(_xlfn.TEXTSPLIT($D37, "-"), 3))</f>
+      <c r="C37" s="95" t="str" cm="1">
+        <f t="array" ref="C37">UPPER(INDEX(_xlfn.TEXTSPLIT($F37, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D37" s="80" t="s">
@@ -16184,8 +16185,8 @@
       <c r="B38" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="74" t="str" cm="1">
-        <f t="array" ref="C38">UPPER(INDEX(_xlfn.TEXTSPLIT($D38, "-"), 3))</f>
+      <c r="C38" s="95" t="str" cm="1">
+        <f t="array" ref="C38">UPPER(INDEX(_xlfn.TEXTSPLIT($F38, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D38" s="80" t="s">
@@ -16273,8 +16274,8 @@
       <c r="B39" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="74" t="str" cm="1">
-        <f t="array" ref="C39">UPPER(INDEX(_xlfn.TEXTSPLIT($D39, "-"), 3))</f>
+      <c r="C39" s="95" t="str" cm="1">
+        <f t="array" ref="C39">UPPER(INDEX(_xlfn.TEXTSPLIT($F39, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D39" s="80" t="s">
@@ -16362,8 +16363,8 @@
       <c r="B40" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="74" t="str" cm="1">
-        <f t="array" ref="C40">UPPER(INDEX(_xlfn.TEXTSPLIT($D40, "-"), 3))</f>
+      <c r="C40" s="95" t="str" cm="1">
+        <f t="array" ref="C40">UPPER(INDEX(_xlfn.TEXTSPLIT($F40, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D40" s="80" t="s">
@@ -16451,8 +16452,8 @@
       <c r="B41" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="74" t="str" cm="1">
-        <f t="array" ref="C41">UPPER(INDEX(_xlfn.TEXTSPLIT($D41, "-"), 3))</f>
+      <c r="C41" s="95" t="str" cm="1">
+        <f t="array" ref="C41">UPPER(INDEX(_xlfn.TEXTSPLIT($F41, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D41" s="80" t="s">
@@ -16540,8 +16541,8 @@
       <c r="B42" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C42" s="74" t="str" cm="1">
-        <f t="array" ref="C42">UPPER(INDEX(_xlfn.TEXTSPLIT($D42, "-"), 3))</f>
+      <c r="C42" s="95" t="str" cm="1">
+        <f t="array" ref="C42">UPPER(INDEX(_xlfn.TEXTSPLIT($F42, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D42" s="80" t="s">
@@ -16629,8 +16630,8 @@
       <c r="B43" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="74" t="str" cm="1">
-        <f t="array" ref="C43">UPPER(INDEX(_xlfn.TEXTSPLIT($D43, "-"), 3))</f>
+      <c r="C43" s="95" t="str" cm="1">
+        <f t="array" ref="C43">UPPER(INDEX(_xlfn.TEXTSPLIT($F43, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D43" s="80" t="s">
@@ -16718,8 +16719,8 @@
       <c r="B44" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C44" s="74" t="str" cm="1">
-        <f t="array" ref="C44">UPPER(INDEX(_xlfn.TEXTSPLIT($D44, "-"), 3))</f>
+      <c r="C44" s="95" t="str" cm="1">
+        <f t="array" ref="C44">UPPER(INDEX(_xlfn.TEXTSPLIT($F44, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D44" s="80" t="s">
@@ -16807,8 +16808,8 @@
       <c r="B45" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C45" s="74" t="str" cm="1">
-        <f t="array" ref="C45">UPPER(INDEX(_xlfn.TEXTSPLIT($D45, "-"), 3))</f>
+      <c r="C45" s="95" t="str" cm="1">
+        <f t="array" ref="C45">UPPER(INDEX(_xlfn.TEXTSPLIT($F45, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D45" s="80" t="s">
@@ -16896,8 +16897,8 @@
       <c r="B46" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C46" s="74" t="str" cm="1">
-        <f t="array" ref="C46">UPPER(INDEX(_xlfn.TEXTSPLIT($D46, "-"), 3))</f>
+      <c r="C46" s="95" t="str" cm="1">
+        <f t="array" ref="C46">UPPER(INDEX(_xlfn.TEXTSPLIT($F46, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D46" s="80" t="s">
@@ -16985,8 +16986,8 @@
       <c r="B47" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="74" t="str" cm="1">
-        <f t="array" ref="C47">UPPER(INDEX(_xlfn.TEXTSPLIT($D47, "-"), 3))</f>
+      <c r="C47" s="95" t="str" cm="1">
+        <f t="array" ref="C47">UPPER(INDEX(_xlfn.TEXTSPLIT($F47, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D47" s="80" t="s">
@@ -17074,8 +17075,8 @@
       <c r="B48" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="74" t="str" cm="1">
-        <f t="array" ref="C48">UPPER(INDEX(_xlfn.TEXTSPLIT($D48, "-"), 3))</f>
+      <c r="C48" s="95" t="str" cm="1">
+        <f t="array" ref="C48">UPPER(INDEX(_xlfn.TEXTSPLIT($F48, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D48" s="80" t="s">
@@ -17163,8 +17164,8 @@
       <c r="B49" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C49" s="74" t="str" cm="1">
-        <f t="array" ref="C49">UPPER(INDEX(_xlfn.TEXTSPLIT($D49, "-"), 3))</f>
+      <c r="C49" s="95" t="str" cm="1">
+        <f t="array" ref="C49">UPPER(INDEX(_xlfn.TEXTSPLIT($F49, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D49" s="80" t="s">
@@ -17252,8 +17253,8 @@
       <c r="B50" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C50" s="74" t="str" cm="1">
-        <f t="array" ref="C50">UPPER(INDEX(_xlfn.TEXTSPLIT($D50, "-"), 3))</f>
+      <c r="C50" s="95" t="str" cm="1">
+        <f t="array" ref="C50">UPPER(INDEX(_xlfn.TEXTSPLIT($F50, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D50" s="80" t="s">
@@ -17341,8 +17342,8 @@
       <c r="B51" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C51" s="74" t="str" cm="1">
-        <f t="array" ref="C51">UPPER(INDEX(_xlfn.TEXTSPLIT($D51, "-"), 3))</f>
+      <c r="C51" s="95" t="str" cm="1">
+        <f t="array" ref="C51">UPPER(INDEX(_xlfn.TEXTSPLIT($F51, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D51" s="80" t="s">
@@ -17430,8 +17431,8 @@
       <c r="B52" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C52" s="74" t="str" cm="1">
-        <f t="array" ref="C52">UPPER(INDEX(_xlfn.TEXTSPLIT($D52, "-"), 3))</f>
+      <c r="C52" s="95" t="str" cm="1">
+        <f t="array" ref="C52">UPPER(INDEX(_xlfn.TEXTSPLIT($F52, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D52" s="80" t="s">
@@ -17519,8 +17520,8 @@
       <c r="B53" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C53" s="74" t="str" cm="1">
-        <f t="array" ref="C53">UPPER(INDEX(_xlfn.TEXTSPLIT($D53, "-"), 3))</f>
+      <c r="C53" s="95" t="str" cm="1">
+        <f t="array" ref="C53">UPPER(INDEX(_xlfn.TEXTSPLIT($F53, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D53" s="80" t="s">
@@ -17608,8 +17609,8 @@
       <c r="B54" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C54" s="74" t="str" cm="1">
-        <f t="array" ref="C54">UPPER(INDEX(_xlfn.TEXTSPLIT($D54, "-"), 3))</f>
+      <c r="C54" s="95" t="str" cm="1">
+        <f t="array" ref="C54">UPPER(INDEX(_xlfn.TEXTSPLIT($F54, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D54" s="80" t="s">
@@ -17697,8 +17698,8 @@
       <c r="B55" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C55" s="74" t="str" cm="1">
-        <f t="array" ref="C55">UPPER(INDEX(_xlfn.TEXTSPLIT($D55, "-"), 3))</f>
+      <c r="C55" s="95" t="str" cm="1">
+        <f t="array" ref="C55">UPPER(INDEX(_xlfn.TEXTSPLIT($F55, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D55" s="80" t="s">
@@ -17786,8 +17787,8 @@
       <c r="B56" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C56" s="74" t="str" cm="1">
-        <f t="array" ref="C56">UPPER(INDEX(_xlfn.TEXTSPLIT($D56, "-"), 3))</f>
+      <c r="C56" s="95" t="str" cm="1">
+        <f t="array" ref="C56">UPPER(INDEX(_xlfn.TEXTSPLIT($F56, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D56" s="80" t="s">
@@ -17875,8 +17876,8 @@
       <c r="B57" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C57" s="74" t="str" cm="1">
-        <f t="array" ref="C57">UPPER(INDEX(_xlfn.TEXTSPLIT($D57, "-"), 3))</f>
+      <c r="C57" s="95" t="str" cm="1">
+        <f t="array" ref="C57">UPPER(INDEX(_xlfn.TEXTSPLIT($F57, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D57" s="80" t="s">
@@ -17964,8 +17965,8 @@
       <c r="B58" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C58" s="74" t="str" cm="1">
-        <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($D58, "-"), 3))</f>
+      <c r="C58" s="95" t="str" cm="1">
+        <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($F58, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D58" s="80" t="s">
@@ -18053,8 +18054,8 @@
       <c r="B59" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C59" s="74" t="str" cm="1">
-        <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($D59, "-"), 3))</f>
+      <c r="C59" s="95" t="str" cm="1">
+        <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($F59, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D59" s="80" t="s">
@@ -18142,8 +18143,8 @@
       <c r="B60" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C60" s="74" t="str" cm="1">
-        <f t="array" ref="C60">UPPER(INDEX(_xlfn.TEXTSPLIT($D60, "-"), 3))</f>
+      <c r="C60" s="95" t="str" cm="1">
+        <f t="array" ref="C60">UPPER(INDEX(_xlfn.TEXTSPLIT($F60, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D60" s="80" t="s">
@@ -18231,8 +18232,8 @@
       <c r="B61" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C61" s="74" t="str" cm="1">
-        <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($D61, "-"), 3))</f>
+      <c r="C61" s="95" t="str" cm="1">
+        <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($F61, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D61" s="80" t="s">
@@ -18320,8 +18321,8 @@
       <c r="B62" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C62" s="74" t="str" cm="1">
-        <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($D62, "-"), 3))</f>
+      <c r="C62" s="95" t="str" cm="1">
+        <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($F62, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D62" s="80" t="s">
@@ -18409,8 +18410,8 @@
       <c r="B63" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C63" s="74" t="str" cm="1">
-        <f t="array" ref="C63">UPPER(INDEX(_xlfn.TEXTSPLIT($D63, "-"), 3))</f>
+      <c r="C63" s="95" t="str" cm="1">
+        <f t="array" ref="C63">UPPER(INDEX(_xlfn.TEXTSPLIT($F63, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D63" s="80" t="s">
@@ -18498,8 +18499,8 @@
       <c r="B64" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C64" s="74" t="str" cm="1">
-        <f t="array" ref="C64">UPPER(INDEX(_xlfn.TEXTSPLIT($D64, "-"), 3))</f>
+      <c r="C64" s="95" t="str" cm="1">
+        <f t="array" ref="C64">UPPER(INDEX(_xlfn.TEXTSPLIT($F64, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D64" s="80" t="s">
@@ -18587,8 +18588,8 @@
       <c r="B65" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C65" s="74" t="str" cm="1">
-        <f t="array" ref="C65">UPPER(INDEX(_xlfn.TEXTSPLIT($D65, "-"), 3))</f>
+      <c r="C65" s="95" t="str" cm="1">
+        <f t="array" ref="C65">UPPER(INDEX(_xlfn.TEXTSPLIT($F65, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D65" s="80" t="s">
@@ -18676,8 +18677,8 @@
       <c r="B66" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C66" s="74" t="str" cm="1">
-        <f t="array" ref="C66">UPPER(INDEX(_xlfn.TEXTSPLIT($D66, "-"), 3))</f>
+      <c r="C66" s="95" t="str" cm="1">
+        <f t="array" ref="C66">UPPER(INDEX(_xlfn.TEXTSPLIT($F66, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D66" s="80" t="s">
@@ -18765,8 +18766,8 @@
       <c r="B67" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C67" s="74" t="str" cm="1">
-        <f t="array" ref="C67">UPPER(INDEX(_xlfn.TEXTSPLIT($D67, "-"), 3))</f>
+      <c r="C67" s="95" t="str" cm="1">
+        <f t="array" ref="C67">UPPER(INDEX(_xlfn.TEXTSPLIT($F67, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D67" s="80" t="s">
@@ -18854,8 +18855,8 @@
       <c r="B68" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C68" s="74" t="str" cm="1">
-        <f t="array" ref="C68">UPPER(INDEX(_xlfn.TEXTSPLIT($D68, "-"), 3))</f>
+      <c r="C68" s="95" t="str" cm="1">
+        <f t="array" ref="C68">UPPER(INDEX(_xlfn.TEXTSPLIT($F68, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D68" s="80" t="s">
@@ -18943,8 +18944,8 @@
       <c r="B69" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C69" s="74" t="str" cm="1">
-        <f t="array" ref="C69">UPPER(INDEX(_xlfn.TEXTSPLIT($D69, "-"), 3))</f>
+      <c r="C69" s="95" t="str" cm="1">
+        <f t="array" ref="C69">UPPER(INDEX(_xlfn.TEXTSPLIT($F69, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D69" s="80" t="s">
@@ -19032,8 +19033,8 @@
       <c r="B70" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="74" t="str" cm="1">
-        <f t="array" ref="C70">UPPER(INDEX(_xlfn.TEXTSPLIT($D70, "-"), 3))</f>
+      <c r="C70" s="95" t="str" cm="1">
+        <f t="array" ref="C70">UPPER(INDEX(_xlfn.TEXTSPLIT($F70, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D70" s="80" t="s">
@@ -19121,8 +19122,8 @@
       <c r="B71" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C71" s="74" t="str" cm="1">
-        <f t="array" ref="C71">UPPER(INDEX(_xlfn.TEXTSPLIT($D71, "-"), 3))</f>
+      <c r="C71" s="95" t="str" cm="1">
+        <f t="array" ref="C71">UPPER(INDEX(_xlfn.TEXTSPLIT($F71, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D71" s="80" t="s">
@@ -19210,8 +19211,8 @@
       <c r="B72" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C72" s="74" t="str" cm="1">
-        <f t="array" ref="C72">UPPER(INDEX(_xlfn.TEXTSPLIT($D72, "-"), 3))</f>
+      <c r="C72" s="95" t="str" cm="1">
+        <f t="array" ref="C72">UPPER(INDEX(_xlfn.TEXTSPLIT($F72, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D72" s="80" t="s">
@@ -19299,8 +19300,8 @@
       <c r="B73" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C73" s="74" t="str" cm="1">
-        <f t="array" ref="C73">UPPER(INDEX(_xlfn.TEXTSPLIT($D73, "-"), 3))</f>
+      <c r="C73" s="95" t="str" cm="1">
+        <f t="array" ref="C73">UPPER(INDEX(_xlfn.TEXTSPLIT($F73, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D73" s="80" t="s">
@@ -19388,8 +19389,8 @@
       <c r="B74" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C74" s="74" t="str" cm="1">
-        <f t="array" ref="C74">UPPER(INDEX(_xlfn.TEXTSPLIT($D74, "-"), 3))</f>
+      <c r="C74" s="95" t="str" cm="1">
+        <f t="array" ref="C74">UPPER(INDEX(_xlfn.TEXTSPLIT($F74, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D74" s="80" t="s">
@@ -19477,8 +19478,8 @@
       <c r="B75" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C75" s="74" t="str" cm="1">
-        <f t="array" ref="C75">UPPER(INDEX(_xlfn.TEXTSPLIT($D75, "-"), 3))</f>
+      <c r="C75" s="95" t="str" cm="1">
+        <f t="array" ref="C75">UPPER(INDEX(_xlfn.TEXTSPLIT($F75, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D75" s="80" t="s">
@@ -19566,8 +19567,8 @@
       <c r="B76" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C76" s="74" t="str" cm="1">
-        <f t="array" ref="C76">UPPER(INDEX(_xlfn.TEXTSPLIT($D76, "-"), 3))</f>
+      <c r="C76" s="95" t="str" cm="1">
+        <f t="array" ref="C76">UPPER(INDEX(_xlfn.TEXTSPLIT($F76, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D76" s="80" t="s">
@@ -19655,8 +19656,8 @@
       <c r="B77" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C77" s="74" t="str" cm="1">
-        <f t="array" ref="C77">UPPER(INDEX(_xlfn.TEXTSPLIT($D77, "-"), 3))</f>
+      <c r="C77" s="95" t="str" cm="1">
+        <f t="array" ref="C77">UPPER(INDEX(_xlfn.TEXTSPLIT($F77, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D77" s="80" t="s">
@@ -19744,8 +19745,8 @@
       <c r="B78" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C78" s="74" t="str" cm="1">
-        <f t="array" ref="C78">UPPER(INDEX(_xlfn.TEXTSPLIT($D78, "-"), 3))</f>
+      <c r="C78" s="95" t="str" cm="1">
+        <f t="array" ref="C78">UPPER(INDEX(_xlfn.TEXTSPLIT($F78, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D78" s="80" t="s">
@@ -19833,8 +19834,8 @@
       <c r="B79" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C79" s="74" t="str" cm="1">
-        <f t="array" ref="C79">UPPER(INDEX(_xlfn.TEXTSPLIT($D79, "-"), 3))</f>
+      <c r="C79" s="95" t="str" cm="1">
+        <f t="array" ref="C79">UPPER(INDEX(_xlfn.TEXTSPLIT($F79, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D79" s="80" t="s">
@@ -19922,8 +19923,8 @@
       <c r="B80" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C80" s="74" t="str" cm="1">
-        <f t="array" ref="C80">UPPER(INDEX(_xlfn.TEXTSPLIT($D80, "-"), 3))</f>
+      <c r="C80" s="95" t="str" cm="1">
+        <f t="array" ref="C80">UPPER(INDEX(_xlfn.TEXTSPLIT($F80, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D80" s="80" t="s">
@@ -20011,8 +20012,8 @@
       <c r="B81" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C81" s="74" t="str" cm="1">
-        <f t="array" ref="C81">UPPER(INDEX(_xlfn.TEXTSPLIT($D81, "-"), 3))</f>
+      <c r="C81" s="95" t="str" cm="1">
+        <f t="array" ref="C81">UPPER(INDEX(_xlfn.TEXTSPLIT($F81, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D81" s="80" t="s">
@@ -20100,8 +20101,8 @@
       <c r="B82" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C82" s="74" t="str" cm="1">
-        <f t="array" ref="C82">UPPER(INDEX(_xlfn.TEXTSPLIT($D82, "-"), 3))</f>
+      <c r="C82" s="95" t="str" cm="1">
+        <f t="array" ref="C82">UPPER(INDEX(_xlfn.TEXTSPLIT($F82, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D82" s="80" t="s">
@@ -20189,8 +20190,8 @@
       <c r="B83" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C83" s="74" t="str" cm="1">
-        <f t="array" ref="C83">UPPER(INDEX(_xlfn.TEXTSPLIT($D83, "-"), 3))</f>
+      <c r="C83" s="95" t="str" cm="1">
+        <f t="array" ref="C83">UPPER(INDEX(_xlfn.TEXTSPLIT($F83, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D83" s="80" t="s">
@@ -20278,8 +20279,8 @@
       <c r="B84" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C84" s="74" t="str" cm="1">
-        <f t="array" ref="C84">UPPER(INDEX(_xlfn.TEXTSPLIT($D84, "-"), 3))</f>
+      <c r="C84" s="95" t="str" cm="1">
+        <f t="array" ref="C84">UPPER(INDEX(_xlfn.TEXTSPLIT($F84, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D84" s="80" t="s">
@@ -20367,8 +20368,8 @@
       <c r="B85" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C85" s="74" t="str" cm="1">
-        <f t="array" ref="C85">UPPER(INDEX(_xlfn.TEXTSPLIT($D85, "-"), 3))</f>
+      <c r="C85" s="95" t="str" cm="1">
+        <f t="array" ref="C85">UPPER(INDEX(_xlfn.TEXTSPLIT($F85, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D85" s="80" t="s">
@@ -20456,8 +20457,8 @@
       <c r="B86" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C86" s="74" t="str" cm="1">
-        <f t="array" ref="C86">UPPER(INDEX(_xlfn.TEXTSPLIT($D86, "-"), 3))</f>
+      <c r="C86" s="95" t="str" cm="1">
+        <f t="array" ref="C86">UPPER(INDEX(_xlfn.TEXTSPLIT($F86, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D86" s="80" t="s">
@@ -20545,8 +20546,8 @@
       <c r="B87" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C87" s="74" t="str" cm="1">
-        <f t="array" ref="C87">UPPER(INDEX(_xlfn.TEXTSPLIT($D87, "-"), 3))</f>
+      <c r="C87" s="95" t="str" cm="1">
+        <f t="array" ref="C87">UPPER(INDEX(_xlfn.TEXTSPLIT($F87, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D87" s="80" t="s">
@@ -20634,8 +20635,8 @@
       <c r="B88" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C88" s="74" t="str" cm="1">
-        <f t="array" ref="C88">UPPER(INDEX(_xlfn.TEXTSPLIT($D88, "-"), 3))</f>
+      <c r="C88" s="95" t="str" cm="1">
+        <f t="array" ref="C88">UPPER(INDEX(_xlfn.TEXTSPLIT($F88, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D88" s="80" t="s">
@@ -20723,8 +20724,8 @@
       <c r="B89" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C89" s="74" t="str" cm="1">
-        <f t="array" ref="C89">UPPER(INDEX(_xlfn.TEXTSPLIT($D89, "-"), 3))</f>
+      <c r="C89" s="95" t="str" cm="1">
+        <f t="array" ref="C89">UPPER(INDEX(_xlfn.TEXTSPLIT($F89, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D89" s="80" t="s">
@@ -20812,8 +20813,8 @@
       <c r="B90" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C90" s="74" t="str" cm="1">
-        <f t="array" ref="C90">UPPER(INDEX(_xlfn.TEXTSPLIT($D90, "-"), 3))</f>
+      <c r="C90" s="95" t="str" cm="1">
+        <f t="array" ref="C90">UPPER(INDEX(_xlfn.TEXTSPLIT($F90, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D90" s="80" t="s">
@@ -20901,8 +20902,8 @@
       <c r="B91" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C91" s="74" t="str" cm="1">
-        <f t="array" ref="C91">UPPER(INDEX(_xlfn.TEXTSPLIT($D91, "-"), 3))</f>
+      <c r="C91" s="95" t="str" cm="1">
+        <f t="array" ref="C91">UPPER(INDEX(_xlfn.TEXTSPLIT($F91, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D91" s="80" t="s">
@@ -20990,8 +20991,8 @@
       <c r="B92" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C92" s="74" t="str" cm="1">
-        <f t="array" ref="C92">UPPER(INDEX(_xlfn.TEXTSPLIT($D92, "-"), 3))</f>
+      <c r="C92" s="95" t="str" cm="1">
+        <f t="array" ref="C92">UPPER(INDEX(_xlfn.TEXTSPLIT($F92, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D92" s="80" t="s">
@@ -21079,8 +21080,8 @@
       <c r="B93" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C93" s="74" t="str" cm="1">
-        <f t="array" ref="C93">UPPER(INDEX(_xlfn.TEXTSPLIT($D93, "-"), 3))</f>
+      <c r="C93" s="95" t="str" cm="1">
+        <f t="array" ref="C93">UPPER(INDEX(_xlfn.TEXTSPLIT($F93, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D93" s="80" t="s">
@@ -21168,8 +21169,8 @@
       <c r="B94" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C94" s="74" t="str" cm="1">
-        <f t="array" ref="C94">UPPER(INDEX(_xlfn.TEXTSPLIT($D94, "-"), 3))</f>
+      <c r="C94" s="95" t="str" cm="1">
+        <f t="array" ref="C94">UPPER(INDEX(_xlfn.TEXTSPLIT($F94, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D94" s="80" t="s">
@@ -21257,8 +21258,8 @@
       <c r="B95" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C95" s="74" t="str" cm="1">
-        <f t="array" ref="C95">UPPER(INDEX(_xlfn.TEXTSPLIT($D95, "-"), 3))</f>
+      <c r="C95" s="95" t="str" cm="1">
+        <f t="array" ref="C95">UPPER(INDEX(_xlfn.TEXTSPLIT($F95, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D95" s="80" t="s">
@@ -21346,8 +21347,8 @@
       <c r="B96" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C96" s="74" t="str" cm="1">
-        <f t="array" ref="C96">UPPER(INDEX(_xlfn.TEXTSPLIT($D96, "-"), 3))</f>
+      <c r="C96" s="95" t="str" cm="1">
+        <f t="array" ref="C96">UPPER(INDEX(_xlfn.TEXTSPLIT($F96, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D96" s="80" t="s">
@@ -21435,8 +21436,8 @@
       <c r="B97" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C97" s="74" t="str" cm="1">
-        <f t="array" ref="C97">UPPER(INDEX(_xlfn.TEXTSPLIT($D97, "-"), 3))</f>
+      <c r="C97" s="95" t="str" cm="1">
+        <f t="array" ref="C97">UPPER(INDEX(_xlfn.TEXTSPLIT($F97, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D97" s="80" t="s">
@@ -21524,8 +21525,8 @@
       <c r="B98" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C98" s="74" t="str" cm="1">
-        <f t="array" ref="C98">UPPER(INDEX(_xlfn.TEXTSPLIT($D98, "-"), 3))</f>
+      <c r="C98" s="95" t="str" cm="1">
+        <f t="array" ref="C98">UPPER(INDEX(_xlfn.TEXTSPLIT($F98, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D98" s="80" t="s">
@@ -21613,8 +21614,8 @@
       <c r="B99" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C99" s="74" t="str" cm="1">
-        <f t="array" ref="C99">UPPER(INDEX(_xlfn.TEXTSPLIT($D99, "-"), 3))</f>
+      <c r="C99" s="95" t="str" cm="1">
+        <f t="array" ref="C99">UPPER(INDEX(_xlfn.TEXTSPLIT($F99, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D99" s="80" t="s">
@@ -21702,8 +21703,8 @@
       <c r="B100" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C100" s="74" t="str" cm="1">
-        <f t="array" ref="C100">UPPER(INDEX(_xlfn.TEXTSPLIT($D100, "-"), 3))</f>
+      <c r="C100" s="95" t="str" cm="1">
+        <f t="array" ref="C100">UPPER(INDEX(_xlfn.TEXTSPLIT($F100, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D100" s="80" t="s">
@@ -21791,8 +21792,8 @@
       <c r="B101" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C101" s="74" t="str" cm="1">
-        <f t="array" ref="C101">UPPER(INDEX(_xlfn.TEXTSPLIT($D101, "-"), 3))</f>
+      <c r="C101" s="95" t="str" cm="1">
+        <f t="array" ref="C101">UPPER(INDEX(_xlfn.TEXTSPLIT($F101, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D101" s="80" t="s">
@@ -21880,8 +21881,8 @@
       <c r="B102" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C102" s="74" t="str" cm="1">
-        <f t="array" ref="C102">UPPER(INDEX(_xlfn.TEXTSPLIT($D102, "-"), 3))</f>
+      <c r="C102" s="95" t="str" cm="1">
+        <f t="array" ref="C102">UPPER(INDEX(_xlfn.TEXTSPLIT($F102, "-"), 3))</f>
         <v>DTG</v>
       </c>
       <c r="D102" s="80" t="s">
@@ -21969,8 +21970,8 @@
       <c r="B103" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C103" s="74" t="str" cm="1">
-        <f t="array" ref="C103">UPPER(INDEX(_xlfn.TEXTSPLIT($D103, "-"), 3))</f>
+      <c r="C103" s="95" t="str" cm="1">
+        <f t="array" ref="C103">UPPER(INDEX(_xlfn.TEXTSPLIT($F103, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D103" s="80" t="s">
@@ -22058,8 +22059,8 @@
       <c r="B104" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C104" s="74" t="str" cm="1">
-        <f t="array" ref="C104">UPPER(INDEX(_xlfn.TEXTSPLIT($D104, "-"), 3))</f>
+      <c r="C104" s="95" t="str" cm="1">
+        <f t="array" ref="C104">UPPER(INDEX(_xlfn.TEXTSPLIT($F104, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D104" s="80" t="s">
@@ -22147,8 +22148,8 @@
       <c r="B105" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C105" s="74" t="str" cm="1">
-        <f t="array" ref="C105">UPPER(INDEX(_xlfn.TEXTSPLIT($D105, "-"), 3))</f>
+      <c r="C105" s="95" t="str" cm="1">
+        <f t="array" ref="C105">UPPER(INDEX(_xlfn.TEXTSPLIT($F105, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D105" s="80" t="s">
@@ -22236,8 +22237,8 @@
       <c r="B106" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C106" s="74" t="str" cm="1">
-        <f t="array" ref="C106">UPPER(INDEX(_xlfn.TEXTSPLIT($D106, "-"), 3))</f>
+      <c r="C106" s="95" t="str" cm="1">
+        <f t="array" ref="C106">UPPER(INDEX(_xlfn.TEXTSPLIT($F106, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D106" s="80" t="s">
@@ -22325,8 +22326,8 @@
       <c r="B107" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C107" s="74" t="str" cm="1">
-        <f t="array" ref="C107">UPPER(INDEX(_xlfn.TEXTSPLIT($D107, "-"), 3))</f>
+      <c r="C107" s="95" t="str" cm="1">
+        <f t="array" ref="C107">UPPER(INDEX(_xlfn.TEXTSPLIT($F107, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D107" s="80" t="s">
@@ -22414,8 +22415,8 @@
       <c r="B108" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C108" s="74" t="str" cm="1">
-        <f t="array" ref="C108">UPPER(INDEX(_xlfn.TEXTSPLIT($D108, "-"), 3))</f>
+      <c r="C108" s="95" t="str" cm="1">
+        <f t="array" ref="C108">UPPER(INDEX(_xlfn.TEXTSPLIT($F108, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D108" s="80" t="s">
@@ -22503,8 +22504,8 @@
       <c r="B109" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C109" s="74" t="str" cm="1">
-        <f t="array" ref="C109">UPPER(INDEX(_xlfn.TEXTSPLIT($D109, "-"), 3))</f>
+      <c r="C109" s="95" t="str" cm="1">
+        <f t="array" ref="C109">UPPER(INDEX(_xlfn.TEXTSPLIT($F109, "-"), 3))</f>
         <v>IF</v>
       </c>
       <c r="D109" s="80" t="s">
@@ -22592,8 +22593,8 @@
       <c r="B110" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C110" s="74" t="str" cm="1">
-        <f t="array" ref="C110">UPPER(INDEX(_xlfn.TEXTSPLIT($D110, "-"), 3))</f>
+      <c r="C110" s="95" t="str" cm="1">
+        <f t="array" ref="C110">UPPER(INDEX(_xlfn.TEXTSPLIT($F110, "-"), 3))</f>
         <v>IF</v>
       </c>
       <c r="D110" s="80" t="s">
@@ -22681,8 +22682,8 @@
       <c r="B111" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C111" s="74" t="str" cm="1">
-        <f t="array" ref="C111">UPPER(INDEX(_xlfn.TEXTSPLIT($D111, "-"), 3))</f>
+      <c r="C111" s="95" t="str" cm="1">
+        <f t="array" ref="C111">UPPER(INDEX(_xlfn.TEXTSPLIT($F111, "-"), 3))</f>
         <v>IF</v>
       </c>
       <c r="D111" s="80" t="s">
@@ -22770,8 +22771,8 @@
       <c r="B112" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C112" s="74" t="str" cm="1">
-        <f t="array" ref="C112">UPPER(INDEX(_xlfn.TEXTSPLIT($D112, "-"), 3))</f>
+      <c r="C112" s="95" t="str" cm="1">
+        <f t="array" ref="C112">UPPER(INDEX(_xlfn.TEXTSPLIT($F112, "-"), 3))</f>
         <v>IF</v>
       </c>
       <c r="D112" s="80" t="s">
@@ -22859,8 +22860,8 @@
       <c r="B113" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C113" s="74" t="str" cm="1">
-        <f t="array" ref="C113">UPPER(INDEX(_xlfn.TEXTSPLIT($D113, "-"), 3))</f>
+      <c r="C113" s="95" t="str" cm="1">
+        <f t="array" ref="C113">UPPER(INDEX(_xlfn.TEXTSPLIT($F113, "-"), 3))</f>
         <v>IF</v>
       </c>
       <c r="D113" s="80" t="s">
@@ -22948,8 +22949,8 @@
       <c r="B114" s="74" t="s">
         <v>1100</v>
       </c>
-      <c r="C114" s="74" t="str" cm="1">
-        <f t="array" ref="C114">UPPER(INDEX(_xlfn.TEXTSPLIT($D114, "-"), 3))</f>
+      <c r="C114" s="95" t="str" cm="1">
+        <f t="array" ref="C114">UPPER(INDEX(_xlfn.TEXTSPLIT($F114, "-"), 3))</f>
         <v>MON</v>
       </c>
       <c r="D114" s="80" t="s">
@@ -23037,8 +23038,8 @@
       <c r="B115" s="74" t="s">
         <v>1100</v>
       </c>
-      <c r="C115" s="74" t="str" cm="1">
-        <f t="array" ref="C115">UPPER(INDEX(_xlfn.TEXTSPLIT($D115, "-"), 3))</f>
+      <c r="C115" s="95" t="str" cm="1">
+        <f t="array" ref="C115">UPPER(INDEX(_xlfn.TEXTSPLIT($F115, "-"), 3))</f>
         <v>MON</v>
       </c>
       <c r="D115" s="80" t="s">
@@ -23126,8 +23127,8 @@
       <c r="B116" s="74" t="s">
         <v>1100</v>
       </c>
-      <c r="C116" s="74" t="str" cm="1">
-        <f t="array" ref="C116">UPPER(INDEX(_xlfn.TEXTSPLIT($D116, "-"), 3))</f>
+      <c r="C116" s="95" t="str" cm="1">
+        <f t="array" ref="C116">UPPER(INDEX(_xlfn.TEXTSPLIT($F116, "-"), 3))</f>
         <v>MON</v>
       </c>
       <c r="D116" s="80" t="s">
@@ -23215,8 +23216,8 @@
       <c r="B117" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C117" s="74" t="str" cm="1">
-        <f t="array" ref="C117">UPPER(INDEX(_xlfn.TEXTSPLIT($D117, "-"), 3))</f>
+      <c r="C117" s="95" t="str" cm="1">
+        <f t="array" ref="C117">UPPER(INDEX(_xlfn.TEXTSPLIT($F117, "-"), 3))</f>
         <v>IF</v>
       </c>
       <c r="D117" s="80" t="s">
@@ -23303,7 +23304,10 @@
       <c r="B118" s="102" t="s">
         <v>1046</v>
       </c>
-      <c r="C118" s="102"/>
+      <c r="C118" s="102" t="str" cm="1">
+        <f t="array" ref="C118">UPPER(INDEX(_xlfn.TEXTSPLIT($F118, "-"), 3))</f>
+        <v>IF</v>
+      </c>
       <c r="D118" s="102" t="s">
         <v>972</v>
       </c>
@@ -23386,7 +23390,10 @@
       <c r="B119" s="102" t="s">
         <v>1046</v>
       </c>
-      <c r="C119" s="102"/>
+      <c r="C119" s="102" t="str" cm="1">
+        <f t="array" ref="C119">UPPER(INDEX(_xlfn.TEXTSPLIT($F119, "-"), 3))</f>
+        <v>IF</v>
+      </c>
       <c r="D119" s="102" t="s">
         <v>972</v>
       </c>
@@ -23470,8 +23477,8 @@
       <c r="B120" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C120" s="74" t="str" cm="1">
-        <f t="array" ref="C120">UPPER(INDEX(_xlfn.TEXTSPLIT($D120, "-"), 3))</f>
+      <c r="C120" s="95" t="str" cm="1">
+        <f t="array" ref="C120">UPPER(INDEX(_xlfn.TEXTSPLIT($F120, "-"), 3))</f>
         <v>CS</v>
       </c>
       <c r="D120" s="80" t="s">
@@ -23559,8 +23566,8 @@
       <c r="B121" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C121" s="74" t="str" cm="1">
-        <f t="array" ref="C121">UPPER(INDEX(_xlfn.TEXTSPLIT($D121, "-"), 3))</f>
+      <c r="C121" s="95" t="str" cm="1">
+        <f t="array" ref="C121">UPPER(INDEX(_xlfn.TEXTSPLIT($F121, "-"), 3))</f>
         <v>CS</v>
       </c>
       <c r="D121" s="80" t="s">
@@ -23648,8 +23655,8 @@
       <c r="B122" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C122" s="74" t="str" cm="1">
-        <f t="array" ref="C122">UPPER(INDEX(_xlfn.TEXTSPLIT($D122, "-"), 3))</f>
+      <c r="C122" s="95" t="str" cm="1">
+        <f t="array" ref="C122">UPPER(INDEX(_xlfn.TEXTSPLIT($F122, "-"), 3))</f>
         <v>CS</v>
       </c>
       <c r="D122" s="80" t="s">
@@ -23737,8 +23744,8 @@
       <c r="B123" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C123" s="74" t="str" cm="1">
-        <f t="array" ref="C123">UPPER(INDEX(_xlfn.TEXTSPLIT($D123, "-"), 3))</f>
+      <c r="C123" s="95" t="str" cm="1">
+        <f t="array" ref="C123">UPPER(INDEX(_xlfn.TEXTSPLIT($F123, "-"), 3))</f>
         <v>CS</v>
       </c>
       <c r="D123" s="80" t="s">
@@ -23826,8 +23833,8 @@
       <c r="B124" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C124" s="74" t="str" cm="1">
-        <f t="array" ref="C124">UPPER(INDEX(_xlfn.TEXTSPLIT($D124, "-"), 3))</f>
+      <c r="C124" s="95" t="str" cm="1">
+        <f t="array" ref="C124">UPPER(INDEX(_xlfn.TEXTSPLIT($F124, "-"), 3))</f>
         <v>CS</v>
       </c>
       <c r="D124" s="80" t="s">
@@ -23915,8 +23922,8 @@
       <c r="B125" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C125" s="74" t="str" cm="1">
-        <f t="array" ref="C125">UPPER(INDEX(_xlfn.TEXTSPLIT($D125, "-"), 3))</f>
+      <c r="C125" s="95" t="str" cm="1">
+        <f t="array" ref="C125">UPPER(INDEX(_xlfn.TEXTSPLIT($F125, "-"), 3))</f>
         <v>CS</v>
       </c>
       <c r="D125" s="80" t="s">
@@ -24004,8 +24011,8 @@
       <c r="B126" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C126" s="74" t="str" cm="1">
-        <f t="array" ref="C126">UPPER(INDEX(_xlfn.TEXTSPLIT($D126, "-"), 3))</f>
+      <c r="C126" s="95" t="str" cm="1">
+        <f t="array" ref="C126">UPPER(INDEX(_xlfn.TEXTSPLIT($F126, "-"), 3))</f>
         <v>DOIP</v>
       </c>
       <c r="D126" s="74" t="s">
@@ -24093,8 +24100,8 @@
       <c r="B127" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C127" s="74" t="str" cm="1">
-        <f t="array" ref="C127">UPPER(INDEX(_xlfn.TEXTSPLIT($D127, "-"), 3))</f>
+      <c r="C127" s="95" t="str" cm="1">
+        <f t="array" ref="C127">UPPER(INDEX(_xlfn.TEXTSPLIT($F127, "-"), 3))</f>
         <v>DOIP</v>
       </c>
       <c r="D127" s="74" t="s">
@@ -24182,8 +24189,8 @@
       <c r="B128" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C128" s="74" t="str" cm="1">
-        <f t="array" ref="C128">UPPER(INDEX(_xlfn.TEXTSPLIT($D128, "-"), 3))</f>
+      <c r="C128" s="95" t="str" cm="1">
+        <f t="array" ref="C128">UPPER(INDEX(_xlfn.TEXTSPLIT($F128, "-"), 3))</f>
         <v>DOIP</v>
       </c>
       <c r="D128" s="74" t="s">
@@ -24271,8 +24278,8 @@
       <c r="B129" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C129" s="74" t="str" cm="1">
-        <f t="array" ref="C129">UPPER(INDEX(_xlfn.TEXTSPLIT($D129, "-"), 3))</f>
+      <c r="C129" s="95" t="str" cm="1">
+        <f t="array" ref="C129">UPPER(INDEX(_xlfn.TEXTSPLIT($F129, "-"), 3))</f>
         <v>DOIP</v>
       </c>
       <c r="D129" s="74" t="s">
@@ -24360,8 +24367,8 @@
       <c r="B130" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C130" s="74" t="str" cm="1">
-        <f t="array" ref="C130">UPPER(INDEX(_xlfn.TEXTSPLIT($D130, "-"), 3))</f>
+      <c r="C130" s="95" t="str" cm="1">
+        <f t="array" ref="C130">UPPER(INDEX(_xlfn.TEXTSPLIT($F130, "-"), 3))</f>
         <v>DOIP</v>
       </c>
       <c r="D130" s="74" t="s">
@@ -24449,8 +24456,8 @@
       <c r="B131" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C131" s="74" t="str" cm="1">
-        <f t="array" ref="C131">UPPER(INDEX(_xlfn.TEXTSPLIT($D131, "-"), 3))</f>
+      <c r="C131" s="95" t="str" cm="1">
+        <f t="array" ref="C131">UPPER(INDEX(_xlfn.TEXTSPLIT($F131, "-"), 3))</f>
         <v>DOIP</v>
       </c>
       <c r="D131" s="74" t="s">
@@ -24538,8 +24545,8 @@
       <c r="B132" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C132" s="74" t="str" cm="1">
-        <f t="array" ref="C132">UPPER(INDEX(_xlfn.TEXTSPLIT($D132, "-"), 3))</f>
+      <c r="C132" s="95" t="str" cm="1">
+        <f t="array" ref="C132">UPPER(INDEX(_xlfn.TEXTSPLIT($F132, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D132" s="80" t="s">
@@ -24627,8 +24634,8 @@
       <c r="B133" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C133" s="74" t="str" cm="1">
-        <f t="array" ref="C133">UPPER(INDEX(_xlfn.TEXTSPLIT($D133, "-"), 3))</f>
+      <c r="C133" s="95" t="str" cm="1">
+        <f t="array" ref="C133">UPPER(INDEX(_xlfn.TEXTSPLIT($F133, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D133" s="80" t="s">
@@ -24716,8 +24723,8 @@
       <c r="B134" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C134" s="74" t="str" cm="1">
-        <f t="array" ref="C134">UPPER(INDEX(_xlfn.TEXTSPLIT($D134, "-"), 3))</f>
+      <c r="C134" s="95" t="str" cm="1">
+        <f t="array" ref="C134">UPPER(INDEX(_xlfn.TEXTSPLIT($F134, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D134" s="80" t="s">
@@ -24805,8 +24812,8 @@
       <c r="B135" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C135" s="74" t="str" cm="1">
-        <f t="array" ref="C135">UPPER(INDEX(_xlfn.TEXTSPLIT($D135, "-"), 3))</f>
+      <c r="C135" s="95" t="str" cm="1">
+        <f t="array" ref="C135">UPPER(INDEX(_xlfn.TEXTSPLIT($F135, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D135" s="80" t="s">
@@ -24894,8 +24901,8 @@
       <c r="B136" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C136" s="74" t="str" cm="1">
-        <f t="array" ref="C136">UPPER(INDEX(_xlfn.TEXTSPLIT($D136, "-"), 3))</f>
+      <c r="C136" s="95" t="str" cm="1">
+        <f t="array" ref="C136">UPPER(INDEX(_xlfn.TEXTSPLIT($F136, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D136" s="80" t="s">
@@ -24983,8 +24990,8 @@
       <c r="B137" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C137" s="74" t="str" cm="1">
-        <f t="array" ref="C137">UPPER(INDEX(_xlfn.TEXTSPLIT($D137, "-"), 3))</f>
+      <c r="C137" s="95" t="str" cm="1">
+        <f t="array" ref="C137">UPPER(INDEX(_xlfn.TEXTSPLIT($F137, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D137" s="80" t="s">
@@ -25072,8 +25079,8 @@
       <c r="B138" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C138" s="74" t="str" cm="1">
-        <f t="array" ref="C138">UPPER(INDEX(_xlfn.TEXTSPLIT($D138, "-"), 3))</f>
+      <c r="C138" s="95" t="str" cm="1">
+        <f t="array" ref="C138">UPPER(INDEX(_xlfn.TEXTSPLIT($F138, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D138" s="80" t="s">
@@ -25161,9 +25168,9 @@
       <c r="B139" s="74" t="s">
         <v>1100</v>
       </c>
-      <c r="C139" s="74" t="str" cm="1">
-        <f t="array" ref="C139">UPPER(INDEX(_xlfn.TEXTSPLIT($D139, "-"), 3))</f>
-        <v>COMM</v>
+      <c r="C139" s="95" t="str" cm="1">
+        <f t="array" ref="C139">UPPER(INDEX(_xlfn.TEXTSPLIT($F139, "-"), 3))</f>
+        <v>COM</v>
       </c>
       <c r="D139" s="80" t="s">
         <v>231</v>
@@ -25250,9 +25257,9 @@
       <c r="B140" s="74" t="s">
         <v>1100</v>
       </c>
-      <c r="C140" s="74" t="str" cm="1">
-        <f t="array" ref="C140">UPPER(INDEX(_xlfn.TEXTSPLIT($D140, "-"), 3))</f>
-        <v>COMM</v>
+      <c r="C140" s="95" t="str" cm="1">
+        <f t="array" ref="C140">UPPER(INDEX(_xlfn.TEXTSPLIT($F140, "-"), 3))</f>
+        <v>COM</v>
       </c>
       <c r="D140" s="80" t="s">
         <v>231</v>
@@ -25340,7 +25347,7 @@
         <v>1100</v>
       </c>
       <c r="C141" s="95" t="str" cm="1">
-        <f t="array" ref="C141">UPPER(INDEX(_xlfn.TEXTSPLIT($D141, "-"), 3))</f>
+        <f t="array" ref="C141">UPPER(INDEX(_xlfn.TEXTSPLIT($F141, "-"), 3))</f>
         <v>SEC</v>
       </c>
       <c r="D141" s="95" t="s">
@@ -25429,7 +25436,7 @@
         <v>1100</v>
       </c>
       <c r="C142" s="95" t="str" cm="1">
-        <f t="array" ref="C142">UPPER(INDEX(_xlfn.TEXTSPLIT($D142, "-"), 3))</f>
+        <f t="array" ref="C142">UPPER(INDEX(_xlfn.TEXTSPLIT($F142, "-"), 3))</f>
         <v>SEC</v>
       </c>
       <c r="D142" s="95" t="s">
@@ -25517,8 +25524,8 @@
         <v>1100</v>
       </c>
       <c r="C143" s="95" t="str" cm="1">
-        <f t="array" ref="C143">UPPER(INDEX(_xlfn.TEXTSPLIT($D143, "-"), 3))</f>
-        <v>COMM</v>
+        <f t="array" ref="C143">UPPER(INDEX(_xlfn.TEXTSPLIT($F143, "-"), 3))</f>
+        <v>COM</v>
       </c>
       <c r="D143" s="95" t="s">
         <v>231</v>
@@ -33658,8 +33665,8 @@
         <v>1100</v>
       </c>
       <c r="C152" s="74" t="str" cm="1">
-        <f t="array" ref="C152">UPPER(INDEX(_xlfn.TEXTSPLIT($D152, "-"), 3))</f>
-        <v>COMM</v>
+        <f t="array" ref="C152">UPPER(INDEX(_xlfn.TEXTSPLIT($F152, "-"), 3))</f>
+        <v>COM</v>
       </c>
       <c r="D152" s="80" t="s">
         <v>231</v>
@@ -33710,9 +33717,9 @@
       <c r="B153" s="73" t="s">
         <v>1100</v>
       </c>
-      <c r="C153" s="73" t="str" cm="1">
-        <f t="array" ref="C153">UPPER(INDEX(_xlfn.TEXTSPLIT($D153, "-"), 3))</f>
-        <v>COMM</v>
+      <c r="C153" s="120" t="str" cm="1">
+        <f t="array" ref="C153">UPPER(INDEX(_xlfn.TEXTSPLIT($F153, "-"), 3))</f>
+        <v>COM</v>
       </c>
       <c r="D153" s="78" t="s">
         <v>231</v>
@@ -33764,7 +33771,7 @@
         <v>1100</v>
       </c>
       <c r="C154" s="74" t="str" cm="1">
-        <f t="array" ref="C154">UPPER(INDEX(_xlfn.TEXTSPLIT($D154, "-"), 3))</f>
+        <f t="array" ref="C154">UPPER(INDEX(_xlfn.TEXTSPLIT($F154, "-"), 3))</f>
         <v>SEC</v>
       </c>
       <c r="D154" s="80" t="s">
@@ -33817,7 +33824,7 @@
         <v>1100</v>
       </c>
       <c r="C155" s="120" t="str" cm="1">
-        <f t="array" ref="C155">UPPER(INDEX(_xlfn.TEXTSPLIT($D155, "-"), 3))</f>
+        <f t="array" ref="C155">UPPER(INDEX(_xlfn.TEXTSPLIT($F155, "-"), 3))</f>
         <v>SEC</v>
       </c>
       <c r="D155" s="121" t="s">
@@ -33869,8 +33876,8 @@
         <v>1100</v>
       </c>
       <c r="C156" s="74" t="str" cm="1">
-        <f t="array" ref="C156">UPPER(INDEX(_xlfn.TEXTSPLIT($D156, "-"), 3))</f>
-        <v>COMM</v>
+        <f t="array" ref="C156">UPPER(INDEX(_xlfn.TEXTSPLIT($F156, "-"), 3))</f>
+        <v>COM</v>
       </c>
       <c r="D156" s="80" t="s">
         <v>231</v>
@@ -33917,6 +33924,7 @@
       <c r="R156" s="74"/>
     </row>
   </sheetData>
+  <autoFilter ref="B1:R156" xr:uid="{52F281E7-0665-4BB7-80DB-4208A01A998B}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -47044,21 +47052,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -47202,10 +47195,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -47227,19 +47245,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>